--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-09-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
-	GetHandleVerifier [0x0x7ff7a66f3150+79584]
-	(No symbol) [0x0x7ff7a64701ba]
-	(No symbol) [0x0x7ff7a64c8067]
-	(No symbol) [0x0x7ff7a64c832c]
-	(No symbol) [0x0x7ff7a651be27]
-	(No symbol) [0x0x7ff7a64f074f]
-	(No symbol) [0x0x7ff7a6518b8b]
-	(No symbol) [0x0x7ff7a64f04e3]
-	(No symbol) [0x0x7ff7a64b8e92]
-	(No symbol) [0x0x7ff7a64b9c63]
-	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
-	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
-	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
-	GetHandleVerifier [0x0x7ff7a670d60e+187294]
-	GetHandleVerifier [0x0x7ff7a671557f+219919]
-	GetHandleVerifier [0x0x7ff7a66fc294+116772]
-	GetHandleVerifier [0x0x7ff7a66fc449+117209]
-	GetHandleVerifier [0x0x7ff7a66e2618+11176]
+	GetHandleVerifier [0x0x7ff62bd330f5+79493]
+	GetHandleVerifier [0x0x7ff62bd33150+79584]
+	(No symbol) [0x0x7ff62bab01ba]
+	(No symbol) [0x0x7ff62bb08067]
+	(No symbol) [0x0x7ff62bb0832c]
+	(No symbol) [0x0x7ff62bb5be27]
+	(No symbol) [0x0x7ff62bb3074f]
+	(No symbol) [0x0x7ff62bb58b8b]
+	(No symbol) [0x0x7ff62bb304e3]
+	(No symbol) [0x0x7ff62baf8e92]
+	(No symbol) [0x0x7ff62baf9c63]
+	GetHandleVerifier [0x0x7ff62bff0dbd+2954061]
+	GetHandleVerifier [0x0x7ff62bfeb02a+2930106]
+	GetHandleVerifier [0x0x7ff62c00b357+3061991]
+	GetHandleVerifier [0x0x7ff62bd4d60e+187294]
+	GetHandleVerifier [0x0x7ff62bd5557f+219919]
+	GetHandleVerifier [0x0x7ff62bd3c294+116772]
+	GetHandleVerifier [0x0x7ff62bd3c449+117209]
+	GetHandleVerifier [0x0x7ff62bd22618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
